--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.65244048561264</v>
+        <v>3.843521578912055</v>
       </c>
       <c r="D2" t="n">
-        <v>21.77411270872218</v>
+        <v>3.538293315167354</v>
       </c>
       <c r="E2" t="n">
-        <v>8.517825462809563</v>
+        <v>1.384146637706554</v>
       </c>
       <c r="F2" t="n">
-        <v>7.365926121081598</v>
+        <v>1.19696299467576</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.53802655347186</v>
+        <v>4.799929314939178</v>
       </c>
       <c r="D3" t="n">
-        <v>28.25042802998346</v>
+        <v>4.590694554872313</v>
       </c>
       <c r="E3" t="n">
-        <v>8.517825462809563</v>
+        <v>1.384146637706554</v>
       </c>
       <c r="F3" t="n">
-        <v>7.365926121081598</v>
+        <v>1.19696299467576</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.72603964766819</v>
+        <v>6.780481442746082</v>
       </c>
       <c r="D4" t="n">
-        <v>33.91852677260557</v>
+        <v>5.511760600548405</v>
       </c>
       <c r="E4" t="n">
-        <v>8.517825462809563</v>
+        <v>1.384146637706554</v>
       </c>
       <c r="F4" t="n">
-        <v>7.365926121081598</v>
+        <v>1.19696299467576</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.13138396265457</v>
+        <v>7.333849893931369</v>
       </c>
       <c r="D5" t="n">
-        <v>43.31780309872399</v>
+        <v>7.039143003542649</v>
       </c>
       <c r="E5" t="n">
-        <v>8.517825462809563</v>
+        <v>1.384146637706554</v>
       </c>
       <c r="F5" t="n">
-        <v>7.365926121081598</v>
+        <v>1.19696299467576</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.62429455327944</v>
+        <v>4.32644786490791</v>
       </c>
       <c r="D6" t="n">
-        <v>26.68937097135008</v>
+        <v>4.337022782844388</v>
       </c>
       <c r="E6" t="n">
-        <v>8.517825462809563</v>
+        <v>1.384146637706554</v>
       </c>
       <c r="F6" t="n">
-        <v>7.365926121081598</v>
+        <v>1.19696299467576</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
